--- a/src/SpkSnbp/SpkSnbp.Web/wwwroot/file/Template_Ekstrakurikuler.xlsx
+++ b/src/SpkSnbp/SpkSnbp.Web/wwwroot/file/Template_Ekstrakurikuler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F20E772-34F2-4C87-B9F9-5B7D5A96DF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95594CF-E5D9-4DE5-BF21-DCE199ACE2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,11 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Nama</t>
   </si>
@@ -36,9 +35,6 @@
   </si>
   <si>
     <t>Tahun Ajaran</t>
-  </si>
-  <si>
-    <t>(C5) Ekstrakurikuler</t>
   </si>
   <si>
     <t>Predikat</t>
@@ -414,16 +410,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="5" width="15" customWidth="1"/>
-    <col min="6" max="9" width="24" customWidth="1"/>
+    <col min="6" max="8" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -439,16 +435,13 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="G1" s="3"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-    </row>
-    <row r="2" spans="1:9">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="2"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -457,9 +450,8 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9">
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="2"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -468,9 +460,8 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:9">
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="2"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -479,9 +470,8 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:9">
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="2"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -490,9 +480,8 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:9">
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="2"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -501,9 +490,8 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="1:9">
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="2"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -512,9 +500,8 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:9">
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="2"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -523,9 +510,8 @@
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:9">
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="2"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -534,9 +520,8 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" spans="1:9">
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="2"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -545,9 +530,8 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="1:9">
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="2"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -556,9 +540,8 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:9">
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="2"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -567,9 +550,8 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9">
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="2"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -578,9 +560,8 @@
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9">
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="2"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -589,9 +570,8 @@
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="1:9">
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="2"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -600,9 +580,8 @@
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:9">
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="2"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -611,9 +590,8 @@
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="1:9">
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="2"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -622,9 +600,8 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="1:9">
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="2"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -633,9 +610,8 @@
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" spans="1:9">
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="2"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -644,9 +620,8 @@
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="1:9">
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="2"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -655,9 +630,8 @@
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-    </row>
-    <row r="21" spans="1:9">
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="2"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -666,9 +640,8 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="22" spans="1:9">
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="2"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -677,9 +650,8 @@
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="23" spans="1:9">
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="2"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -688,9 +660,8 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-    </row>
-    <row r="24" spans="1:9">
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="2"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -699,9 +670,8 @@
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" spans="1:9">
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="2"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -710,9 +680,8 @@
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-    </row>
-    <row r="26" spans="1:9">
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="2"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -721,9 +690,8 @@
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" spans="1:9">
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="2"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -732,9 +700,8 @@
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-    </row>
-    <row r="28" spans="1:9">
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="2"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -743,9 +710,8 @@
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-    </row>
-    <row r="29" spans="1:9">
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="2"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -754,9 +720,8 @@
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-    </row>
-    <row r="30" spans="1:9">
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="2"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -765,9 +730,8 @@
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-    </row>
-    <row r="31" spans="1:9">
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="2"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -776,9 +740,8 @@
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-    </row>
-    <row r="32" spans="1:9">
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="2"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -787,9 +750,8 @@
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-    </row>
-    <row r="33" spans="1:9">
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="2"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -798,9 +760,8 @@
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-    </row>
-    <row r="34" spans="1:9">
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="2"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -809,9 +770,8 @@
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-    </row>
-    <row r="35" spans="1:9">
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="2"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -820,9 +780,8 @@
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-    </row>
-    <row r="36" spans="1:9">
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="2"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -831,9 +790,8 @@
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-    </row>
-    <row r="37" spans="1:9">
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="2"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -842,11 +800,10 @@
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="F1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/SpkSnbp/SpkSnbp.Web/wwwroot/file/Template_Ekstrakurikuler.xlsx
+++ b/src/SpkSnbp/SpkSnbp.Web/wwwroot/file/Template_Ekstrakurikuler.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Videos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95594CF-E5D9-4DE5-BF21-DCE199ACE2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74DC5908-6E9D-4E8B-AC3F-65B826544E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,43 +22,83 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
-    <t>Nama</t>
+    <t>No</t>
   </si>
   <si>
-    <t>NISN</t>
+    <t>Nama Siswa</t>
   </si>
   <si>
-    <t>Jurusan</t>
+    <t>Ekstrakurikuler yang Diikuti</t>
   </si>
   <si>
-    <t>Kelas</t>
+    <t>Predikat Akhir</t>
   </si>
   <si>
-    <t>Tahun Ajaran</t>
+    <t>Rekapitulasi Ekstrakurikuler</t>
   </si>
   <si>
-    <t>Predikat</t>
+    <t>Kompetensi Keahlian</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -81,24 +121,96 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyBorder="1"/>
+    <xf numFmtId="41" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
+    <cellStyle name="Comma [0] 2" xfId="2" xr:uid="{3786B6F6-8002-40C3-A41F-EF7DE40EAD15}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{03AAA9A6-1192-49A9-BF0A-C6A1A9FB5E89}"/>
+    <cellStyle name="Normal 3" xfId="1" xr:uid="{B7EB68E9-A38D-4753-A55B-026B65760717}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -410,400 +522,559 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:H53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="5" width="15" customWidth="1"/>
-    <col min="6" max="8" width="24" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="10"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>1</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="2"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="2"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="3"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="2"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="3"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="2"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="3"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="2"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="3"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="2"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="3"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="2"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="2"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="3"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="2"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="3"/>
       <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="2"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="3"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="2"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="3"/>
       <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="2"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="3"/>
       <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="2"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="3"/>
       <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="2"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="3"/>
       <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="2"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="3"/>
       <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="2"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="3"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="2"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="3"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="2"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="3"/>
       <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="2"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="3"/>
       <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="2"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="3"/>
       <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="2"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="3"/>
       <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="2"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="3"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="2"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="3"/>
       <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="2"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="3"/>
       <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="2"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="3"/>
       <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="2"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="3"/>
       <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="2"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="3"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="2"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="3"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="2"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="3"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="2"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="3"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="2"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="3"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="2"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="3"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+    </row>
+    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+    </row>
+    <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+    </row>
+    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+    </row>
+    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+    </row>
+    <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+    </row>
+    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+    </row>
+    <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+    </row>
+    <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+    </row>
+    <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+    </row>
+    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+    </row>
+    <row r="52" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="1"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+    </row>
+    <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="1"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="F1:H1"/>
+  <mergeCells count="6">
+    <mergeCell ref="F4:H5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="C4:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
